--- a/src/attributions/attributions_ig_traj_467.xlsx
+++ b/src/attributions/attributions_ig_traj_467.xlsx
@@ -1571,25 +1571,25 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06692013671556604</v>
+        <v>0.1318286361418962</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.007698636910770198</v>
+        <v>0.007817734994164091</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01526296678998702</v>
+        <v>-0.03517696102108809</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02375884960327811</v>
+        <v>0.1676855329727245</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.02137050315071144</v>
+        <v>-0.01776865857029999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01006654873820268</v>
+        <v>0.0136690695234335</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
@@ -1622,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0009988672468050383</v>
+        <v>0.04030479376347024</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1634,37 +1634,37 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01745118797245224</v>
+        <v>-0.06092721248345735</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0169785956205028</v>
+        <v>0.02604543077507457</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.004317274279963414</v>
+        <v>-0.0025082137875116</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.007869420444146536</v>
+        <v>-0.02422343590344568</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.001009917385144851</v>
+        <v>2.028998180320486e-05</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1673,13 +1673,13 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01292516747852669</v>
+        <v>0.0656298953568214</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,25 +1688,25 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.009408746994766772</v>
+        <v>0.007537451641716182</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.01465675484797975</v>
+        <v>-0.05488785249186845</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1058366067877649</v>
+        <v>0.3417529928856365</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1715,52 +1715,52 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0082007164108862</v>
+        <v>-0.0715118608064487</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.01673018408105359</v>
+        <v>-0.1007414360251559</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01386038139405156</v>
+        <v>-0.02683617345330867</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.01305096889270698</v>
+        <v>-0.0319026166904537</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.003916014014959461</v>
+        <v>-0.007986276254670261</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03855135551404824</v>
+        <v>0.01901978263206083</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,16 +1769,16 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.02596299839252248</v>
+        <v>0.09202342486906359</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01363593773567502</v>
+        <v>0.07091375573518559</v>
       </c>
       <c r="BR3" t="n">
         <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
@@ -1787,25 +1787,25 @@
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.04160734495829051</v>
+        <v>0.1961805412122276</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.02896190079870664</v>
+        <v>-0.01569918423822938</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.02623374164207505</v>
+        <v>-0.03498834296088231</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
@@ -1814,22 +1814,22 @@
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.01021121588104703</v>
+        <v>-0.06802884885886072</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.002657907976476829</v>
+        <v>0.006880430614843442</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01703656807997285</v>
+        <v>0.042292731036304</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
@@ -1838,55 +1838,55 @@
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01464176343024662</v>
+        <v>-0.05193693535965875</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.005383069586818494</v>
+        <v>0.1007911039616115</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.02528367336834453</v>
+        <v>0.004504584074273084</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.004319751624972959</v>
+        <v>-0.06209336860597533</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.0001546267831410483</v>
+        <v>0.007429280782746868</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0220186973712585</v>
+        <v>0.0484200971685799</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
@@ -1895,25 +1895,25 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.01093068582250599</v>
+        <v>-0.002726282346296123</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.01696039703971827</v>
+        <v>-0.04544014567812261</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.01720814075582321</v>
+        <v>0.07869964151386276</v>
       </c>
       <c r="DK3" t="n">
         <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
@@ -1922,22 +1922,22 @@
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.003040710677854332</v>
+        <v>-0.04765778061487626</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.02257622502596876</v>
+        <v>-0.01336474692719589</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.005797130557044341</v>
+        <v>0.02304619884723903</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
@@ -1949,25 +1949,25 @@
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.02587838974234904</v>
+        <v>0.002804233365923414</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.04498270796651414</v>
+        <v>-0.1020856110394351</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.01469546633585775</v>
+        <v>0.01578824188802605</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>-0</v>
@@ -1976,76 +1976,76 @@
         <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.001173331975195375</v>
+        <v>-0.0009178727080572242</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.01170680737225634</v>
+        <v>-0.02343257450103831</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.00230608257389561</v>
+        <v>-0.006440112272731733</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.00637155468317768</v>
+        <v>-0.01430083630715559</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.0123611003589092</v>
+        <v>-0.113616538792832</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.05772247863443561</v>
+        <v>-0.1421157210232721</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
         <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.000685533797697584</v>
+        <v>-0.07203002191469346</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.0002219075286049679</v>
+        <v>-0.005953772722106577</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.02170245804226252</v>
+        <v>0.03339712365508587</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>0</v>
@@ -2057,64 +2057,64 @@
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.0231384710108488</v>
+        <v>-0.08236326848594332</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.05048600306408532</v>
+        <v>0.04376879064877498</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.007131253066648013</v>
+        <v>0.002233441911127721</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.0004095146174966913</v>
+        <v>0.02791215368997892</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.01160022670605569</v>
+        <v>0.007625445417755534</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.04196190299251346</v>
+        <v>-0.08084680033485234</v>
       </c>
       <c r="FV3" t="n">
         <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.02425752562382387</v>
+        <v>-0.01060100053622391</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,13 +2123,13 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.00639797179176058</v>
+        <v>-0.03277063800963731</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1712863114473656</v>
+        <v>0.1751939360811453</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03796502845542246</v>
+        <v>-0.04845843995259011</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04737848213212567</v>
+        <v>-0.04459680884214391</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,22 +2161,22 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1182888863385793</v>
+        <v>0.1739762052943203</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01192962242350428</v>
+        <v>-0.0218216944881022</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.05944875942275085</v>
+        <v>-0.05621804657388186</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2188,103 +2188,103 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05722972474486246</v>
+        <v>0.05835698155598177</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01046553216889693</v>
+        <v>-0.02972941975870926</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02808469387429977</v>
+        <v>-0.04233074771208535</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01673929346319286</v>
+        <v>-0.01124794075997898</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.01231485737333374</v>
+        <v>-0.01383591440345973</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001694138348302584</v>
+        <v>-0.02978252408723408</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02034157055315556</v>
+        <v>0.07537594595273256</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03344262271137145</v>
+        <v>-0.02310169506775687</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.03887131747375178</v>
+        <v>0.0240341027589725</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3183382078861889</v>
+        <v>0.2592735073806272</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.02115433228579579</v>
+        <v>-0.08899717078722982</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1575356266136382</v>
+        <v>-0.1216363731122356</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
@@ -2293,7 +2293,7 @@
         <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01079562669345964</v>
+        <v>-0.02345784408096589</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.01612422805532911</v>
+        <v>-0.0088472411692118</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.06610050271055802</v>
+        <v>-0.02072410885121132</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.07054037891642595</v>
+        <v>0.008060441278678282</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.05661358910673901</v>
+        <v>0.03361313906912871</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.09449768741576664</v>
+        <v>0.05008167401097176</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,76 +2356,76 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1634579663398945</v>
+        <v>0.2082224711274827</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.00274819160867778</v>
+        <v>-0.06853882880701484</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.02120236475338493</v>
+        <v>-0.04360727738421191</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.05345852274625645</v>
+        <v>-0.08476578863555369</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.005679547297831632</v>
+        <v>0.07122910644885082</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.005306705878183</v>
+        <v>0.01297770761538995</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.03568702633521963</v>
+        <v>-0.04792545386783361</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.04436266335623708</v>
+        <v>0.06312530850314386</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.08634830961935626</v>
+        <v>0.03616863937696731</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.03018420341628278</v>
+        <v>-0.08667842955289698</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0285912201215302</v>
+        <v>0.08050425357776378</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01287203013867217</v>
+        <v>0.02209380492585794</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.04526691187746678</v>
+        <v>-0.07293588807331007</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.01258912294407035</v>
+        <v>0.05583086585992706</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.01316545437119579</v>
+        <v>-0.03249922327164721</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,217 +2491,217 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.03986165864711567</v>
+        <v>-0.04675061875623168</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.05312889245093388</v>
+        <v>0.02436537206116761</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.00752713499362133</v>
+        <v>-0.02426508939670904</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0453389105192584</v>
+        <v>0.02942150923376052</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.05059546115836701</v>
+        <v>0.02919742214260903</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02849456738785242</v>
+        <v>-0.03114455270633319</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.0270548173741125</v>
+        <v>-0.03524770581849452</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.07780448254855828</v>
+        <v>0.06615655836567497</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.05138656114088212</v>
+        <v>0.004922666872664602</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.05515026620620901</v>
+        <v>-0.05714642465155417</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.06399665268745858</v>
+        <v>-0.05492992652875127</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.01804349450838135</v>
+        <v>-0.01441429944918136</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.04776032676788616</v>
+        <v>-0.09612575556957431</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01910302737017021</v>
+        <v>0.07718888421405305</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01137434268864248</v>
+        <v>0.01022996850999029</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.04983481055607748</v>
+        <v>-0.05259181342947356</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.05259301818027051</v>
+        <v>0.03989000610859876</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02626979598803915</v>
+        <v>0.01163847501448609</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.01884386494285135</v>
+        <v>0.00585617356857291</v>
       </c>
       <c r="FR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.02202338409996755</v>
+        <v>0.08079600550967206</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.02353331687864172</v>
+        <v>-0.01977914442428499</v>
       </c>
       <c r="FU4" t="n">
         <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.008929060785395973</v>
+        <v>-0.05419834418832242</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02719958895625641</v>
+        <v>0.01333917475481372</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3278,43 +3278,43 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1967477208947564</v>
+        <v>0.06074873873477344</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.004872265091194075</v>
+        <v>-0.003889759625662089</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02837682393856376</v>
+        <v>-0.01795134019156774</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.116776944234789</v>
+        <v>0.07401433320454719</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006951769056264325</v>
+        <v>0.006255222616555193</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02842913099643884</v>
+        <v>-0.02896193675166796</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3326,25 +3326,25 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06086784869816914</v>
+        <v>0.02791115061291402</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.02034314225616877</v>
+        <v>-0.01852534914657623</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05035320125856222</v>
+        <v>-0.007212291135012052</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
@@ -3356,46 +3356,46 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01267934448369045</v>
+        <v>-0.0007763535266766436</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002797233796791172</v>
+        <v>-0.009997309870422797</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.003174615656739935</v>
+        <v>-0.006334617336254192</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0005254745217937639</v>
+        <v>0.02865225080254765</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.01586140385751073</v>
+        <v>-0.004099014277274058</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.02460788336239492</v>
+        <v>0.02879611932217942</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3410,46 +3410,46 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2836599140785776</v>
+        <v>0.103106628234913</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0247045848605295</v>
+        <v>-0.01526153126348673</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.08781716397491006</v>
+        <v>-0.05437376472816221</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01926705599221756</v>
+        <v>-0.02171106795569198</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.02768828583778542</v>
+        <v>-0.00138151043378305</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03735425356236665</v>
+        <v>-0.008436403021960888</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,19 +3467,19 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.08426837505918107</v>
+        <v>0.02962891895439955</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0101499845918527</v>
+        <v>0.01097400229585997</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1094836136844937</v>
+        <v>0.03773499739817775</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3494,43 +3494,43 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1420761185347105</v>
+        <v>0.07874500860693298</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0152030182012071</v>
+        <v>-0.03178618245802724</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.03775478345620469</v>
+        <v>-0.01731667489793599</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.05586648558837519</v>
+        <v>-0.02599509817344935</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.002971947335261922</v>
+        <v>0.02592973122066764</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.001850693063388636</v>
+        <v>0.01198166808502256</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
@@ -3542,49 +3542,49 @@
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.03330164037527465</v>
+        <v>-0.03216885445670557</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.03118696582035519</v>
+        <v>0.02374778565324595</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.05820720391161267</v>
+        <v>0.02752999858953947</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.03900416094557654</v>
+        <v>-0.02715357645704208</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.008175261877428851</v>
+        <v>0.03169230891224878</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002528719973443893</v>
+        <v>0.01243395333632475</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3593,28 +3593,28 @@
         <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01336814134607777</v>
+        <v>0.002006773222763457</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.03268254201884994</v>
+        <v>0.008751862623341699</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.005690566030630777</v>
+        <v>-0.004074210643828254</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
         <v>-0</v>
@@ -3626,73 +3626,73 @@
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.06801742044870897</v>
+        <v>-0.02897721219882668</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.01833799856181818</v>
+        <v>-0.02196687112483586</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.006270177971182392</v>
+        <v>-0.02243480303804125</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.006914874914832961</v>
+        <v>0.03954358244318998</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.01770957462388867</v>
+        <v>0.01534594124036323</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02682832782717445</v>
+        <v>-0.04256685891871886</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.03187961122065148</v>
+        <v>-0.0002939312962154249</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.006586336872955008</v>
+        <v>0.01854508542456964</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02700006138957949</v>
+        <v>0.02562904105665485</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
@@ -3701,7 +3701,7 @@
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,25 +3710,25 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04093468309117096</v>
+        <v>-0.003390772540662928</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0.006741975655173421</v>
+        <v>0.01929360496863816</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.02487739632918624</v>
+        <v>0.005850265767029958</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>-0</v>
@@ -3737,16 +3737,16 @@
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.04196201217797101</v>
+        <v>-0.03127926856299725</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.002227011316701669</v>
+        <v>0.03558985718803918</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.01594024624359943</v>
+        <v>0.008309137068756431</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3761,55 +3761,55 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0208388691368058</v>
+        <v>0.004855684571395597</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.01883390333143351</v>
+        <v>0.009468266321568697</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01293236814637832</v>
+        <v>-0.02501411470254545</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.04618970860674082</v>
+        <v>0.01800369687857918</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0.03594314514803253</v>
+        <v>0.03589261280069899</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001185876646727552</v>
+        <v>-0.04554940163557047</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
@@ -3818,28 +3818,28 @@
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.00385376722799897</v>
+        <v>0.001132351990417148</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.03462309383010512</v>
+        <v>0.0003829393575601626</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
         <v>0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.195493801821271</v>
+        <v>0.1046992717232178</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.00262433643965683</v>
+        <v>-0.04380932874742949</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1123130265949508</v>
+        <v>-0.04410650431527321</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,25 +3874,25 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1460540106776211</v>
+        <v>0.1666447642936649</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01281029644780225</v>
+        <v>-0.07924692196547506</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.08690718197286153</v>
+        <v>-0.02979805461192514</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009516749568929046</v>
+        <v>0.0351392995173556</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3910,25 +3910,25 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.04213149074306444</v>
+        <v>-0.01367486628839358</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.00875229422033265</v>
+        <v>-0.005739543346307549</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01537375536667186</v>
+        <v>-0.003444705547117668</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -3937,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.008969460895326143</v>
+        <v>-0.02312185662913138</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.001075567528596065</v>
+        <v>-0.00102528233912652</v>
       </c>
       <c r="AH7" t="n">
         <v>-0</v>
@@ -3949,28 +3949,28 @@
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01919028624154192</v>
+        <v>0.03193528172724642</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02452725996030964</v>
+        <v>0.01200728559440222</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.04685764606827698</v>
+        <v>-0.01880411520178354</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,37 +3979,37 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2037734641204624</v>
+        <v>0.1668890881735769</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.01646481092004047</v>
+        <v>-0.0754436014311024</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.103121402873532</v>
+        <v>-0.05637709753255934</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05836311109248396</v>
+        <v>-0.008022095506493455</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,25 +4018,25 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.03041243685794306</v>
+        <v>-0.03756703162716841</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.02888214728328173</v>
+        <v>-0.02008574291188483</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.08977949986049211</v>
+        <v>0.03281655123404687</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
@@ -4045,25 +4045,25 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.04281419079574032</v>
+        <v>0.05111702287706049</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01313708953238299</v>
+        <v>0.002356341240437258</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09209549202766351</v>
+        <v>0.1474744849876853</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.02465785465065819</v>
+        <v>-0.02261716358808872</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0188113852500117</v>
+        <v>-0.02616283810160829</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.04754226287899155</v>
+        <v>-0.05297950397524855</v>
       </c>
       <c r="CF7" t="n">
         <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0103755135045273</v>
+        <v>0.02398914840284505</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.03834580492435055</v>
+        <v>0.04127941148886242</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01345214999114164</v>
+        <v>-0.1003224623350294</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.02039721178057041</v>
+        <v>0.05915831845344691</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.0417184007410606</v>
+        <v>0.05184194605045334</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,79 +4138,79 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03213678433521184</v>
+        <v>-0.04515409070243256</v>
       </c>
       <c r="CX7" t="n">
         <v>-0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.009805329673056182</v>
+        <v>0.0198695842419276</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.038022920070216</v>
+        <v>0.04065539289836598</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.00622528152549361</v>
+        <v>0.0002946167042541655</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.003569384862801263</v>
+        <v>-0.01384719780604454</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-3.222820901262594e-05</v>
+        <v>0.014210996200159</v>
       </c>
       <c r="DK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL7" t="n">
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02169473200569216</v>
+        <v>-0.04143458340804888</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.03408508832012905</v>
+        <v>0.01900951846392074</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.004170221164915911</v>
+        <v>-0.03140237787612263</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -4219,13 +4219,13 @@
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01486740590448314</v>
+        <v>0.02804286185500048</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
@@ -4234,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03673486163849918</v>
+        <v>-0.01078813776041749</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01248081776169925</v>
+        <v>-0.08906677824958563</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -4252,7 +4252,7 @@
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02300870499644768</v>
+        <v>0.01751863618404378</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
@@ -4261,37 +4261,37 @@
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.005710237687450103</v>
+        <v>0.001099032940967893</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02927829074474437</v>
+        <v>0.02885877517086386</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03876350886544885</v>
+        <v>-0.02528451282232739</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.02989406189698851</v>
+        <v>-0.02020284008772543</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.06878887911503173</v>
+        <v>0.04003041067051415</v>
       </c>
       <c r="EU7" t="n">
         <v>-0</v>
@@ -4300,31 +4300,31 @@
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03254807243068258</v>
+        <v>-0.05727337506206529</v>
       </c>
       <c r="EZ7" t="n">
         <v>0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.007394094081075812</v>
+        <v>0.0130671036885425</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.04177928752133848</v>
+        <v>0.03717234128156535</v>
       </c>
       <c r="FD7" t="n">
         <v>-0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01453961554677161</v>
+        <v>-0.04252202547318758</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
@@ -4342,37 +4342,37 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.04340098043238874</v>
+        <v>0.02399432189243665</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.02043022316993903</v>
+        <v>0.005491935027898105</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.01959464406170035</v>
+        <v>0.02414767283404416</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
         <v>0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.02390750666654722</v>
+        <v>-0.0455298128044691</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002320044599917166</v>
+        <v>0.0004942518367445441</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,13 +4381,13 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03007550638754577</v>
+        <v>0.001245589930916076</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
@@ -4399,13 +4399,13 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.02909638141826818</v>
+        <v>0.001197721161351397</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4419,13 +4419,13 @@
         <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.07456227594869803</v>
+        <v>-0.02241409194984206</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2262579093387404</v>
+        <v>0.02763679243337344</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07668622950747261</v>
+        <v>-0.04655912773761502</v>
       </c>
       <c r="F8" t="n">
         <v>-0</v>
@@ -4434,25 +4434,25 @@
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
         <v>-0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
         <v>-0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.09035003424277582</v>
+        <v>-0.02331029320056025</v>
       </c>
       <c r="M8" t="n">
-        <v>0.260863098418725</v>
+        <v>0.02035156450412963</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04626602657923398</v>
+        <v>-0.04457984530414748</v>
       </c>
       <c r="O8" t="n">
         <v>-0</v>
@@ -4461,25 +4461,25 @@
         <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.05559316916798959</v>
+        <v>-0.01042021354461238</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07592653641401946</v>
+        <v>0.03576714197409259</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01854353142418418</v>
+        <v>0.008469050832594402</v>
       </c>
       <c r="X8" t="n">
         <v>-0</v>
@@ -4488,10 +4488,10 @@
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -4500,13 +4500,13 @@
         <v>-0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.009771008800622056</v>
+        <v>-0.0083753897303766</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.01585153559192339</v>
+        <v>-0.0117488241882012</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.02190327240067729</v>
+        <v>-0.01413764935431492</v>
       </c>
       <c r="AG8" t="n">
         <v>-0</v>
@@ -4524,43 +4524,43 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.009423533362920684</v>
+        <v>-0.02516497451196773</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.02590354781923845</v>
+        <v>0.02898185254726592</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.03430777962838209</v>
+        <v>-0.01063515395202387</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.09583536249624817</v>
+        <v>-0.04415671490823063</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.1786988405945926</v>
+        <v>0.0997802213891647</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1862591724634094</v>
+        <v>-0.0829959530493093</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -4581,13 +4581,13 @@
         <v>-0</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.02051622049852461</v>
+        <v>0.0008814114473619391</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.05141479207832069</v>
+        <v>-0.08155054850815077</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.03123479940405085</v>
+        <v>-0.03943867004981953</v>
       </c>
       <c r="BH8" t="n">
         <v>-0</v>
@@ -4596,25 +4596,25 @@
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0556334881966089</v>
+        <v>0.02686907144603846</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0024377403277938</v>
+        <v>0.04567472828132278</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.1521009055218665</v>
+        <v>0.05805410443246959</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
@@ -4623,115 +4623,115 @@
         <v>-0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0.1046079441190873</v>
+        <v>-0.03860128416305073</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.1162344249057741</v>
+        <v>0.105307879039335</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.121759208039611</v>
+        <v>-0.02062829455514074</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
         <v>0</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.05785254690421136</v>
+        <v>0.02801664753842099</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.0604513139156312</v>
+        <v>0.005188006044693146</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01083007273344436</v>
+        <v>0.00997213218549845</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL8" t="n">
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.007496658827611843</v>
+        <v>0.005059132193539757</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.007517122919148013</v>
+        <v>0.03079069968463233</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.06862229069512946</v>
+        <v>0.05283946302255259</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
         <v>-0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.03874822412503003</v>
+        <v>0.02079037349965204</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0.05054640642885559</v>
+        <v>0.004271185150936057</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.01714340891396561</v>
+        <v>0.01726572550443426</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0.002967559385418131</v>
+        <v>0.01309918661658499</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0.06425750300090968</v>
+        <v>-0.02546235286568098</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01327898343284288</v>
+        <v>-0.0001286543994519732</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4764,19 +4764,19 @@
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
         <v>0</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.05421283440306532</v>
+        <v>0.005136205711129674</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.03686665987384669</v>
+        <v>-0.008328679176376802</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.07737948733128533</v>
+        <v>0.02923354851625552</v>
       </c>
       <c r="DS8" t="n">
         <v>-0</v>
@@ -4785,34 +4785,34 @@
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX8" t="n">
         <v>-0</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.02995790768705678</v>
+        <v>-0.02265161384396748</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.03008075542337652</v>
+        <v>-0.0185890423722036</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.03466597758124259</v>
+        <v>-0.02831012231804675</v>
       </c>
       <c r="EB8" t="n">
         <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
@@ -4821,22 +4821,22 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.07115265413713048</v>
+        <v>0.002852775604572641</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.06640823691001121</v>
+        <v>0.0214786795011148</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.03575537329969117</v>
+        <v>-0.006739442564019357</v>
       </c>
       <c r="EK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM8" t="n">
         <v>0</v>
@@ -4845,100 +4845,100 @@
         <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.03498016407504083</v>
+        <v>-0.007471725624693824</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0.05257315105408347</v>
+        <v>-0.01454428703028304</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.009346332934057594</v>
+        <v>0.01154783947509741</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY8" t="n">
         <v>0</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.05282155879327256</v>
+        <v>0.02154800431041581</v>
       </c>
       <c r="FA8" t="n">
-        <v>-0.05867476285528651</v>
+        <v>-0.00566946699457441</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.01632933115529235</v>
+        <v>0.01172408586757103</v>
       </c>
       <c r="FC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE8" t="n">
         <v>-0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.02886968456677217</v>
+        <v>0.03472482244414408</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.04937580179927734</v>
+        <v>-0.009843483220247419</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.05844046550326075</v>
+        <v>-0.03367670443191965</v>
       </c>
       <c r="FL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.006638897624860193</v>
+        <v>-0.001056437208653287</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.005312047427562369</v>
+        <v>0.004295868555555447</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.02022737146092662</v>
+        <v>0.0252730698592184</v>
       </c>
       <c r="FU8" t="n">
         <v>-0</v>
@@ -4947,22 +4947,22 @@
         <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
         <v>-0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.02143107561313182</v>
+        <v>0.01897765326443534</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.03730930171103044</v>
+        <v>-0.04353452908820719</v>
       </c>
       <c r="GC8" t="n">
         <v>0</v>
@@ -4974,10 +4974,10 @@
         <v>0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,22 +5551,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2039042032380843</v>
+        <v>0.1624890108280126</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1794651428754679</v>
+        <v>-0.03517353042275206</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.05426417571395763</v>
+        <v>-0.05604130088587556</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
@@ -5578,37 +5578,37 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1497077258600152</v>
+        <v>0.251104519025754</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1813129142142397</v>
+        <v>-0.0710675130666631</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06132786598334804</v>
+        <v>-0.05180892514067065</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04693461228322</v>
+        <v>0.06317744510012414</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,25 +5617,25 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.02371370407454441</v>
+        <v>-0.06460317993792435</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04871372225115689</v>
+        <v>0.009747609914780613</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02749954987435061</v>
+        <v>-0.02207181338370546</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
@@ -5644,10 +5644,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0005362738560554806</v>
+        <v>-0.06379687752442272</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.008605049747437407</v>
+        <v>0.005166607419836569</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5659,136 +5659,136 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04732359225231512</v>
+        <v>0.01398072897990404</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01548276700525104</v>
+        <v>-0.04570248291524239</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.01970076137404788</v>
+        <v>-0.0225867306381499</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2141488937998984</v>
+        <v>0.290264670291465</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.1062261028739671</v>
+        <v>-0.1324265044963237</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.0451446279529856</v>
+        <v>-0.07959845254784892</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.05173649375456642</v>
+        <v>-0.0359667448786388</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1070129495180789</v>
+        <v>-0.03791549588927695</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.02067427852827511</v>
+        <v>7.913141324252069e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.08977216179274879</v>
+        <v>0.07754645520822853</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02566454218381968</v>
+        <v>0.08519851442063854</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.04807652347252042</v>
+        <v>0.03242034364106194</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1301914605638603</v>
+        <v>0.1781957025448215</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.04762874876486222</v>
+        <v>-0.05258211270698402</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0258906902271311</v>
+        <v>-0.02047873662083436</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,25 +5797,25 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.03271780498461448</v>
+        <v>-0.05942179253702937</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.03436311909200391</v>
+        <v>0.03381907415401052</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02375783740825914</v>
+        <v>0.02664697909378639</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.0214513098871394</v>
+        <v>-0.1095875978177684</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,10 +5833,10 @@
         <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.002208518665768379</v>
+        <v>0.09992244601688334</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.01472796541548929</v>
+        <v>0.002968648043976293</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5851,19 +5851,19 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.01641976526971575</v>
+        <v>-0.05299859485398353</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.03299875652722398</v>
+        <v>0.01309326307506909</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.03151716845135254</v>
+        <v>0.03109656387711999</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
@@ -5875,49 +5875,49 @@
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.0356052353063743</v>
+        <v>-0.04695873188998312</v>
       </c>
       <c r="DG10" t="n">
         <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.02272898681069823</v>
+        <v>-0.02266218589266791</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.004597759484357604</v>
+        <v>-0.01872345834203331</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.02801827752347907</v>
+        <v>-0.02205557932194702</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01870892383402612</v>
+        <v>-0.008257323406525808</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.06810005201429935</v>
+        <v>-0.01853215109101155</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5929,10 +5929,10 @@
         <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.005347577098407808</v>
+        <v>0.03457488949925407</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,37 +5941,37 @@
         <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.05718706211650888</v>
+        <v>-0.02212621060065236</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.04963009826079739</v>
+        <v>0.001631842142773033</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.01647437049456156</v>
+        <v>-0.007891310834109291</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03164526663203931</v>
+        <v>-0.009021288163095791</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.007830312550541641</v>
+        <v>0.03635594799454477</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5980,58 +5980,58 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.02871633323905612</v>
+        <v>0.001633944621082099</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01290487038339589</v>
+        <v>-0.04731795650667259</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.04759833445654382</v>
+        <v>0.02004377189911824</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0124994363199761</v>
+        <v>-0.06691307413105145</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0288083656907957</v>
+        <v>0.02049436982140813</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.03555749521189096</v>
+        <v>0.01932702515407583</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
@@ -6040,7 +6040,7 @@
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.03770862458792774</v>
+        <v>-0.05458349219990931</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,16 +6049,16 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03748858524174518</v>
+        <v>0.08250773167892646</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02218923871449233</v>
+        <v>-0.01045535086384923</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.006739213473433409</v>
+        <v>0.005831272045879421</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,37 +6076,37 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.00412104259029083</v>
+        <v>-0.01598819193376091</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001489320649345486</v>
+        <v>-0.01814803208195101</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02977210585132421</v>
+        <v>-0.06225193092248942</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.04201092091254649</v>
+        <v>0.03612388095777556</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6123,16 +6123,16 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5551579428259135</v>
+        <v>0.4423443329987101</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2425430702317883</v>
+        <v>-0.2232751408864951</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1506766661926395</v>
+        <v>-0.01990668329270999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6150,16 +6150,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4777254912241717</v>
+        <v>0.4940617823599897</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.254909955795878</v>
+        <v>-0.2808597214952874</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2057176965143236</v>
+        <v>-0.05937111514528649</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6177,52 +6177,52 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1525492886119854</v>
+        <v>0.1259770771762188</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.008696073752571903</v>
+        <v>-0.06181921781562294</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0861569961346406</v>
+        <v>-0.09541527577831091</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1166096908266328</v>
+        <v>-0.06933896838975366</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.001190052743659858</v>
+        <v>-0.09074958759991542</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.001429558295255545</v>
+        <v>-0.08768311783926977</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.06626318813998347</v>
+        <v>0.1255236326289956</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.02260921176166639</v>
+        <v>-0.08301526888939309</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02537188921776616</v>
+        <v>0.05179515851053841</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,46 +6255,46 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4988829689007592</v>
+        <v>0.4192209481416405</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.02192413533171946</v>
+        <v>-0.1333158088145006</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.08879036613131305</v>
+        <v>-0.1843462618513573</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.06562038319081129</v>
+        <v>-0.004957123426739756</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.09884545298573308</v>
+        <v>-0.06465157051768569</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.2465476722483913</v>
+        <v>-0.05184017953384308</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,22 +6312,22 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06642904013177818</v>
+        <v>-0.04681740816627369</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.05582315380179269</v>
+        <v>-0.001368661349878034</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.04271239389614757</v>
+        <v>0.07219415775121923</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6339,19 +6339,19 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2827111139446433</v>
+        <v>0.3445311867046899</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.06134877768279721</v>
+        <v>-0.1688681804601636</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.06588681329246723</v>
+        <v>-0.05545085961268199</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,46 +6366,46 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1220913929187614</v>
+        <v>-0.1523844101892461</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.03644679041433904</v>
+        <v>0.1418315563514078</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01216098720746076</v>
+        <v>0.008387757785333226</v>
       </c>
       <c r="CI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.03532412798487509</v>
+        <v>-0.1667370657215068</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.07588559657295625</v>
+        <v>0.2545750530719122</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1131815626625403</v>
+        <v>0.1203537279962039</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6414,28 +6414,28 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1039860629432535</v>
+        <v>-0.1381279837482322</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.05144575046327381</v>
+        <v>0.1463450739232324</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01250496669015023</v>
+        <v>0.01195160837619561</v>
       </c>
       <c r="DA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,19 +6447,19 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.07075867959655732</v>
+        <v>-0.1314114159986926</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.03148961340718454</v>
+        <v>0.02420388734106395</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01798594684873402</v>
+        <v>-0.0898173256911478</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.05655329607467577</v>
+        <v>-0.0795805007774549</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.02918312602971489</v>
+        <v>0.08988818165920079</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.08227551019326146</v>
+        <v>-0.006010251962161577</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6498,25 +6498,25 @@
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.04459618323733418</v>
+        <v>0.04410871229525919</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.03955622728033572</v>
+        <v>-0.05921412088150095</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.02104676492265019</v>
+        <v>0.04570852568851878</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
@@ -6525,52 +6525,52 @@
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.06839024974759757</v>
+        <v>-0.110974284318262</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0560507957411942</v>
+        <v>0.07416703795162087</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0659823016708551</v>
+        <v>0.05288973202695449</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1006079381575802</v>
+        <v>-0.06263967236961035</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.02445448079862796</v>
+        <v>0.06990386406897137</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.03830189902495351</v>
+        <v>-0.04341758257134812</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,112 +6579,112 @@
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1116252403370809</v>
+        <v>-0.1649794554710959</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.06326882975589</v>
+        <v>0.1542467258594135</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.0152529581331342</v>
+        <v>-4.789192131773617e-05</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01762596276331823</v>
+        <v>-0.1166830060267382</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0819593933575707</v>
+        <v>0.1062579569861482</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.0535140285861791</v>
+        <v>0.0333950183918576</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.004948100312100984</v>
+        <v>0.00426830910897864</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.04945673482434494</v>
+        <v>0.06265515741012269</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.00984892657875802</v>
+        <v>-0.02060378258508473</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01866325265970753</v>
+        <v>-0.1578758401997867</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.05540680771825736</v>
+        <v>0.04961188042175001</v>
       </c>
       <c r="GC11" t="n">
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.136454222055864</v>
+        <v>0.3605316616461264</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01528479203520033</v>
+        <v>-0.01284740306534163</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.08468305517941427</v>
+        <v>-0.110953687967528</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,52 +6719,52 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1089476941873885</v>
+        <v>0.5180347744570374</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.02157995454045</v>
+        <v>-0.0842369250711098</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1012959849445551</v>
+        <v>-0.09536055722643852</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01872221616371819</v>
+        <v>0.06216301414393695</v>
       </c>
       <c r="U12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.005072572643909984</v>
+        <v>-0.05124289829321659</v>
       </c>
       <c r="X12" t="n">
-        <v>0.007851978048001527</v>
+        <v>0.005150877943904208</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,22 +6773,22 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01464733222069297</v>
+        <v>0.006257682138970258</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01284472708252207</v>
+        <v>-0.1120400123653476</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.002308036015302659</v>
+        <v>-0.0480472664726933</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6800,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.00639893919951408</v>
+        <v>0.02536720034174513</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.0130531379601332</v>
+        <v>-0.00422816990229901</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.0149756465026066</v>
+        <v>-0.02665948514664977</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,10 +6824,10 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1031832290450098</v>
+        <v>0.3585789156559056</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.01526129238740877</v>
+        <v>-0.1246385541750601</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.03789654662286067</v>
+        <v>-0.05282115130978305</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,61 +6854,61 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.04390811816356971</v>
+        <v>0.04815836152598382</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03211105380045551</v>
+        <v>-0.05578988044105449</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.04650633974858079</v>
+        <v>-0.07714501346013342</v>
       </c>
       <c r="BI12" t="n">
         <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.04528505161976266</v>
+        <v>0.03570243182655668</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.02344144052568435</v>
+        <v>0.06323935324568593</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.008309391879694445</v>
+        <v>-0.008505316151361547</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
         <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.04833610311662011</v>
+        <v>0.2503983350289534</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.0009560583832833554</v>
+        <v>-0.02593598838194241</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.01669313514946856</v>
+        <v>-0.04117606360932714</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6935,7 +6935,7 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.02681092253782091</v>
+        <v>-0.1178929238985295</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,10 +6944,10 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.002923169881238457</v>
+        <v>0.0127405524959386</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.02506784366970084</v>
+        <v>0.05771824469792567</v>
       </c>
       <c r="CJ12" t="n">
         <v>0</v>
@@ -6956,40 +6956,40 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01527299122647187</v>
+        <v>-0.1993297310883153</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.009944480840403223</v>
+        <v>0.09529942226810668</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.009173798030434428</v>
+        <v>0.06048926687668136</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01836816759632294</v>
+        <v>-0.1235158221573166</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.002142826162358466</v>
+        <v>-0.006394246611462298</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.02463259027486274</v>
+        <v>0.05543846617383827</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7013,22 +7013,22 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.026956217337294</v>
+        <v>-0.0593641715983156</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01298530849747217</v>
+        <v>-0.1250744210721377</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0002284061077876941</v>
+        <v>0.01824883729584411</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7037,52 +7037,52 @@
         <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.01922440472735903</v>
+        <v>-0.09438123934199918</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.006791455569243831</v>
+        <v>0.03731298564502118</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.006902419930850502</v>
+        <v>-0.02155982692067258</v>
       </c>
       <c r="DT12" t="n">
         <v>0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01348873540882265</v>
+        <v>0.00228021147270243</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.004748662227946882</v>
+        <v>0.09361861404095849</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0.01418617198553473</v>
+        <v>-0.06932313264343515</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
@@ -7091,52 +7091,52 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.01226905121920143</v>
+        <v>-0.03561105621120701</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
         <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0005463698619766715</v>
+        <v>-0.01984834534004597</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.01482679483973342</v>
+        <v>0.03963272240465405</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.005940816257268848</v>
+        <v>-0.02330301860013907</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.006240349599943447</v>
+        <v>-0.07988897508545831</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0129354837231548</v>
+        <v>0.08315549351913573</v>
       </c>
       <c r="EU12" t="n">
         <v>-0</v>
@@ -7151,34 +7151,34 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.01919260667582262</v>
+        <v>-0.1375034013541365</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.0002256536348331041</v>
+        <v>-0.0129570849998465</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.02780826921091565</v>
+        <v>0.05310948093974181</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.002984358126909825</v>
+        <v>-0.152353588648952</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,37 +7187,37 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01858710004204234</v>
+        <v>0.1025089305317037</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.02192096250131277</v>
+        <v>0.02214332624441886</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>5.725937803713366e-05</v>
+        <v>0.0007638882414780828</v>
       </c>
       <c r="FR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.001414697908836521</v>
+        <v>-0.007398906028835106</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01575460842636233</v>
+        <v>-0.01872508091005732</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7226,25 +7226,25 @@
         <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.01520087879327517</v>
+        <v>-0.04541710459263681</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.01857872799264919</v>
+        <v>0.0002341058744626497</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,16 +7261,16 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9693096854668491</v>
+        <v>0.7997936115904558</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.414675274672283</v>
+        <v>-0.4003713773713442</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2682886518033066</v>
+        <v>-0.1533487514313452</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7288,19 +7288,19 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7343668891176016</v>
+        <v>0.9119030536722249</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3644393913505021</v>
+        <v>-0.5692066855961579</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.289443778789033</v>
+        <v>-0.2957149691399154</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7312,55 +7312,55 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2118320877873702</v>
+        <v>0.1506177262971102</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0888531010048189</v>
+        <v>-0.1695759977231388</v>
       </c>
       <c r="W13" t="n">
-        <v>0.009130579721479948</v>
+        <v>-0.212172803416647</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1137264690819172</v>
+        <v>0.001928085068011257</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.02013651303936857</v>
+        <v>-0.1797241012655184</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.008521876979631497</v>
+        <v>-0.185295803367862</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -7369,16 +7369,16 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.08071388162229773</v>
+        <v>0.2080241003566958</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.05127142038260828</v>
+        <v>-0.1323024722898084</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.06175644199115229</v>
+        <v>0.04887236943983334</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -7393,46 +7393,46 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.7417093965057329</v>
+        <v>0.8747457731009413</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.01503161150749968</v>
+        <v>-0.2348523816039933</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.02440720705154856</v>
+        <v>-0.4052181549589929</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1052567486186746</v>
+        <v>-0.06092860633472751</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.1865210749118863</v>
+        <v>-0.09414108636086042</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.3760090502094713</v>
+        <v>-0.0646662490406308</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
         <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,22 +7450,22 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1565975580897339</v>
+        <v>0.02938779206685446</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.06179874494520846</v>
+        <v>0.01503403923132088</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1239228739715702</v>
+        <v>0.1623669560349012</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7474,22 +7474,22 @@
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.3955293595488003</v>
+        <v>0.5722824584571561</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.02155269506594122</v>
+        <v>-0.3107704285926533</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.02849283945573523</v>
+        <v>-0.1859850006969775</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,46 +7504,46 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1835963516252771</v>
+        <v>-0.2775415392177662</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.06030512554844031</v>
+        <v>0.2042467027310005</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.02551290077223061</v>
+        <v>0.06929566519542713</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001556453858324508</v>
+        <v>-0.3487827263250354</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.1459254453048237</v>
+        <v>0.4134855149783538</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1339840504658734</v>
+        <v>0.1642528823872585</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,55 +7552,55 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1572876102234378</v>
+        <v>-0.252625799000019</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.09613443436881514</v>
+        <v>0.238268848725535</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.03870381335905678</v>
+        <v>0.05357857026306774</v>
       </c>
       <c r="DA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.1404095338064327</v>
+        <v>-0.1256689688668694</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.08827306973852397</v>
+        <v>0.04596548117232043</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01543273145985332</v>
+        <v>-0.1708829102411184</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7612,19 +7612,19 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.1045336833343151</v>
+        <v>-0.1578549275072562</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0.002345394654317209</v>
+        <v>-0.05379538761471944</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.09222144553638345</v>
+        <v>-0.03048570124575328</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7639,76 +7639,76 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.03163902942798742</v>
+        <v>0.1243106925811811</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.01835674355994654</v>
+        <v>0.08981623920520684</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.08090852051140933</v>
+        <v>-0.05491521720269814</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.1307233619536361</v>
+        <v>-0.1362090235997583</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.03835097248113387</v>
+        <v>0.1452022841885748</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.09820357336693178</v>
+        <v>0.07886573034130145</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.09164091844584768</v>
+        <v>-0.09008985698902552</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.06763640335692937</v>
+        <v>0.1323593651724974</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.03160469169765504</v>
+        <v>-0.1019439829667469</v>
       </c>
       <c r="ET13" t="n">
         <v>-0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,46 +7717,46 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1538507231510892</v>
+        <v>-0.2967891440893436</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.08224693608845234</v>
+        <v>0.2473844903794488</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.02425122472207305</v>
+        <v>0.03275859659581886</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.05653952438804526</v>
+        <v>-0.1763714346484337</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.09494218578565053</v>
+        <v>0.2002410250165741</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.06600224145768117</v>
+        <v>0.08126230147696298</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
@@ -7765,25 +7765,25 @@
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0001499803669970135</v>
+        <v>0.001213216318233477</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.04276450373537638</v>
+        <v>0.2352811086939256</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.002101005018160105</v>
+        <v>-0.008500845948620099</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
@@ -7798,31 +7798,31 @@
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.02303666037637804</v>
+        <v>-0.2208798891720963</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.03266810648691743</v>
+        <v>0.1266662222797779</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,19 +7830,19 @@
         <v>-0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.3584263355158025</v>
+        <v>-0.2509767112384328</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07054356519492137</v>
+        <v>-0.005712313160048556</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6757335966407643</v>
+        <v>0.4890093782623005</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7857,19 +7857,19 @@
         <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2815249635663052</v>
+        <v>-0.3242079842320448</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>-0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001076001667134229</v>
+        <v>0.1315558227602506</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6621296652004959</v>
+        <v>0.4977560517456547</v>
       </c>
       <c r="P14" t="n">
         <v>-0</v>
@@ -7884,19 +7884,19 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.02261152973827276</v>
+        <v>-0.1165757483892361</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>-0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04468158215747921</v>
+        <v>0.1544396386451896</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04915980445873799</v>
+        <v>0.05834774303840588</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -7905,25 +7905,25 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.09397738437547734</v>
+        <v>-0.01060400893008473</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.04272001079871132</v>
+        <v>0.2508401875204844</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.04567183750646853</v>
+        <v>0.1716126959671651</v>
       </c>
       <c r="AH14" t="n">
         <v>-0</v>
@@ -7938,22 +7938,22 @@
         <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.04028040565363836</v>
+        <v>-0.08938974722355786</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
         <v>-0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.03343058032541105</v>
+        <v>-0.07141031188667379</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.1013374147220494</v>
+        <v>0.1419350850785697</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -7965,19 +7965,19 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.3496123901370689</v>
+        <v>-0.6149150868424663</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1176416667378131</v>
+        <v>0.05124918492133224</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.4159167410334281</v>
+        <v>0.2723188853781366</v>
       </c>
       <c r="AZ14" t="n">
         <v>-0</v>
@@ -7986,13 +7986,13 @@
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.1363276258712861</v>
+        <v>0.08170203648854645</v>
       </c>
       <c r="BE14" t="n">
         <v>-0</v>
@@ -8001,10 +8001,10 @@
         <v>-0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.07804823697946346</v>
+        <v>0.2336195409683079</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.1334109812523011</v>
+        <v>0.1525195406289848</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
@@ -8016,10 +8016,10 @@
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.06437718804027238</v>
+        <v>-0.02808547196251074</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.05677652824897449</v>
+        <v>-0.1385188322066593</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0167280044953449</v>
+        <v>-0.02112653033162911</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8046,22 +8046,22 @@
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.1814432584153705</v>
+        <v>-0.3609464324788373</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
         <v>-0</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.05096246965670754</v>
+        <v>0.08540976179636547</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.2442437851956338</v>
+        <v>0.2468978629782147</v>
       </c>
       <c r="CA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
@@ -8073,22 +8073,22 @@
         <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.09563317152722253</v>
+        <v>0.1353737942335806</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
         <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.001868486598459206</v>
+        <v>-0.03001118606419656</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0.1280446536226048</v>
+        <v>-0.15401869209775</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
@@ -8100,7 +8100,7 @@
         <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0412637418483278</v>
+        <v>0.2269538224178695</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,13 +8109,13 @@
         <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.09548358933826835</v>
+        <v>-0.2482769967602448</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.03347332754688526</v>
+        <v>-0.2056955870139079</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
@@ -8124,25 +8124,25 @@
         <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.06836744339993493</v>
+        <v>0.1190269201676349</v>
       </c>
       <c r="CX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY14" t="n">
         <v>-0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.005964797800183227</v>
+        <v>-0.02170763906877115</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0.1292388377225533</v>
+        <v>-0.153686291184802</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
         <v>0</v>
@@ -8154,52 +8154,52 @@
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.03522074379844873</v>
+        <v>0.02602821044456436</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.0451292987198296</v>
+        <v>0.143457207551632</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.002096138166662609</v>
+        <v>0.01221123357026819</v>
       </c>
       <c r="DK14" t="n">
         <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.02082847349919064</v>
+        <v>0.05983620482545693</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
         <v>-0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.01169424518701359</v>
+        <v>-0.05691653126968155</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.04839778300533853</v>
+        <v>-0.0194603711054358</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,103 +8208,103 @@
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.01373815011721641</v>
+        <v>-0.08857196490501922</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.04125175225901213</v>
+        <v>-0.02305623465380945</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.03921136714938062</v>
+        <v>-0.09701524717326272</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
         <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.05876603620853781</v>
+        <v>0.01797715629432751</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.06697709981787055</v>
+        <v>0.06633794866875849</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0.1187965508257458</v>
+        <v>-0.04674716205997467</v>
       </c>
       <c r="EL14" t="n">
         <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.05477361947891703</v>
+        <v>0.03522483360979681</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.03807295209295621</v>
+        <v>0.03417440531574344</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0.008960976612050451</v>
+        <v>-0.09140359651574274</v>
       </c>
       <c r="EU14" t="n">
         <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.06711425615821572</v>
+        <v>0.1421204180030103</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.0186092983772505</v>
+        <v>-8.114730177647684e-05</v>
       </c>
       <c r="FC14" t="n">
-        <v>-0.1237551099324788</v>
+        <v>-0.1451321065658844</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
@@ -8316,34 +8316,34 @@
         <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.05165863531889633</v>
+        <v>0.153753685851329</v>
       </c>
       <c r="FI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ14" t="n">
         <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.02357539816790319</v>
+        <v>-0.0412854336283522</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.09284515781444785</v>
+        <v>0.1845761019107228</v>
       </c>
       <c r="FM14" t="n">
         <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP14" t="n">
         <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.003168337348758927</v>
+        <v>0.02953155875099928</v>
       </c>
       <c r="FR14" t="n">
         <v>0</v>
@@ -8352,10 +8352,10 @@
         <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.001305324771699856</v>
+        <v>3.931547984264331e-05</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0.05248366356703922</v>
+        <v>-0.1639671128683699</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
@@ -8364,31 +8364,31 @@
         <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.02371463551229076</v>
+        <v>0.04706252062347626</v>
       </c>
       <c r="GA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB14" t="n">
         <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.03277649065415175</v>
+        <v>-0.001856665556442917</v>
       </c>
       <c r="GE14" t="n">
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8399,49 +8399,49 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4207407582783952</v>
+        <v>0.2894280728202719</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1057680806656078</v>
+        <v>-0.08926589440868546</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06614013104404462</v>
+        <v>0.01104583938908595</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.344898224608627</v>
+        <v>0.3498072053445712</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1246645582748916</v>
+        <v>-0.1381725407518589</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.08548388747449838</v>
+        <v>-0.02471436007606851</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8450,22 +8450,22 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1058243800424973</v>
+        <v>0.05660298421579375</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01415784092786805</v>
+        <v>-0.002986185362387166</v>
       </c>
       <c r="W15" t="n">
-        <v>0.07668508086118024</v>
+        <v>-0.02329246113861204</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
@@ -8477,127 +8477,127 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.09342615938797148</v>
+        <v>-0.03089176053648323</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.01372511832776135</v>
+        <v>-0.130756318587823</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.006778646018672934</v>
+        <v>-0.05857217581944753</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.00726728785169232</v>
+        <v>0.06290588004119031</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.03849531132134775</v>
+        <v>-0.0318219062891698</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.06837206553982138</v>
+        <v>0.011605887206839</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2825432897005961</v>
+        <v>0.2669556041286597</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.01117265865013376</v>
+        <v>-0.1172460173719837</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1050154596940906</v>
+        <v>-0.1158316508064882</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05940438651593592</v>
+        <v>-0.02726102285854659</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.06207979295017589</v>
+        <v>0.008302881253147223</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1125931060130989</v>
+        <v>-0.01632758866613903</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.06001821980777427</v>
+        <v>0.02545269738953294</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.01248016243682259</v>
+        <v>0.009381868430927967</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1742850571410473</v>
+        <v>0.04391918025266035</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
@@ -8609,55 +8609,55 @@
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1413633229110826</v>
+        <v>0.2111108182919833</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.03786953959328373</v>
+        <v>-0.09371528096319073</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08541862479101886</v>
+        <v>0.006265966044022678</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.08509261325521747</v>
+        <v>-0.07618543844134781</v>
       </c>
       <c r="CF15" t="n">
         <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.01069910619404409</v>
+        <v>0.07141080873932081</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.004751237532125739</v>
+        <v>0.01124741693550737</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,52 +8669,52 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.05696423441630818</v>
+        <v>-0.1116100693847247</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.07944349286456209</v>
+        <v>0.1288055883807946</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1119013589346013</v>
+        <v>0.03285217278870046</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.07391771015257588</v>
+        <v>-0.06744018262251143</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.02626905894571118</v>
+        <v>0.07801614593175724</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.006689934287718516</v>
+        <v>0.002148479777851462</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
@@ -8723,211 +8723,211 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.07141853557554</v>
+        <v>-0.06640517256681823</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.01134601792306502</v>
+        <v>0.0443842578812125</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01985261913270829</v>
+        <v>-0.08483807546908673</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.03286758628912744</v>
+        <v>-0.04474990588574503</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.1210160496938121</v>
+        <v>-0.01701446958669111</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.02826847065997855</v>
+        <v>0.01267281363831739</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.07961023745249052</v>
+        <v>0.02476425292604009</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.004064416429594918</v>
+        <v>-0.02473543802547052</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.03293975564082362</v>
+        <v>-0.02094825654053888</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.08502341726040563</v>
+        <v>-0.03586530444938027</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.06066832725731706</v>
+        <v>-0.1374647279043767</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.07269801013394418</v>
+        <v>0.003725484974269903</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.05963753531932518</v>
+        <v>-0.05037276725371485</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.03393832511731459</v>
+        <v>0.02599430558812485</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.02106246991945144</v>
+        <v>-0.0305221342546939</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.0757303959479048</v>
+        <v>-0.08287193041745955</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.008392059306536886</v>
+        <v>0.08069764603186527</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01036374921147554</v>
+        <v>-0.004208828787158637</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.04451910997438841</v>
+        <v>0.08447431107588152</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0492682343527534</v>
+        <v>0.1008781539525718</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.05190337132649394</v>
+        <v>-0.01231577188965889</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.02195518555359808</v>
+        <v>-0.06533093632236288</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.0398098162714226</v>
+        <v>0.04345220117756576</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.008674086492441094</v>
+        <v>0.07668656573105127</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
         <v>-0</v>
@@ -8936,31 +8936,31 @@
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.01907278246302546</v>
+        <v>-0.07285871371061528</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.07891588057507001</v>
+        <v>0.02800803408491075</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
